--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file ADERS (undefined) to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -237,7 +237,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+    <t>Mapping: VA Adverse Drug Event Reporting System (VA ADERS)</t>
   </si>
   <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
@@ -675,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1920: source value from ADERS - 22_PVac1_TypeBrand</t>
+    <t>1920: source value from ADERS - 22_PVac1_TypeBrand (A-22.11)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -783,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t>1926: source value from ADERS - 22_PVac1_Date</t>
+    <t>1926: source value from ADERS - 22_PVac1_Date (A-22.17)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -977,7 +977,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1921: source value from ADERS - 22_PVac1_Mfgr</t>
+    <t>1921: source value from ADERS - 22_PVac1_Mfgr (A-22.12)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -989,7 +989,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1922: source value from ADERS - 22_PVac1_Lot</t>
+    <t>1922: source value from ADERS - 22_PVac1_Lot (A-22.13)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1035,7 +1035,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1924: source value from ADERS - 22_PVac1_Site</t>
+    <t>1924: source value from ADERS - 22_PVac1_Site (A-22.15)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1083,7 +1083,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1923: source value from ADERS - 22_PVac1_Route</t>
+    <t>1923: source value from ADERS - 22_PVac1_Route (A-22.14)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1531,7 +1531,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1925: source value from ADERS - 22_PVac1_DoseInSeries</t>
+    <t>1925: source value from ADERS - 22_PVac1_DoseInSeries (A-22.16)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1895,7 +1895,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="67.44921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="147.5546875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="494">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>\-</t>
+    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,7 +517,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
+    <t>A set of codes indicating the current status of an Immunization.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -548,6 +551,9 @@
     <t>example</t>
   </si>
   <si>
+    <t>The reason why a vaccine was not administered.</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -560,20 +566,16 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine Product Type (bind to CVX)</t>
+    <t>Vaccine product administered</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">us-core-5
-</t>
+    <t>The code for vaccine product administered.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -675,7 +677,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1920: source value from ADERS - 22_PVac1_TypeBrand (A-22.11)</t>
+    <t>1920: source value from ADERS - PVac1_TypeBrand (A-22.11)</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -687,11 +689,7 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -783,7 +781,7 @@
 </t>
   </si>
   <si>
-    <t>1926: source value from ADERS - 22_PVac1_Date (A-22.17)</t>
+    <t>1926: source value from ADERS - PVac1_Date (A-22.17)</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -930,6 +928,9 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -977,7 +978,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1921: source value from ADERS - 22_PVac1_Mfgr (A-22.12)</t>
+    <t>1921: source value from ADERS - PVac1_Mfgr (A-22.12)</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -989,7 +990,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1922: source value from ADERS - 22_PVac1_Lot (A-22.13)</t>
+    <t>1922: source value from ADERS - PVac1_Lot (A-22.13)</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1035,7 +1036,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1924: source value from ADERS - 22_PVac1_Site (A-22.15)</t>
+    <t>1924: source value from ADERS - PVac1_Site (A-22.15)</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1083,7 +1084,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1923: source value from ADERS - 22_PVac1_Route (A-22.14)</t>
+    <t>1923: source value from ADERS - PVac1_Route (A-22.14)</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1531,7 +1532,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1925: source value from ADERS - 22_PVac1_DoseInSeries (A-22.16)</t>
+    <t>1925: source value from ADERS - PVac1_DoseInSeries (A-22.16)</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1870,7 +1871,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1885,7 +1886,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2071,9 +2072,7 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3282,7 +3281,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3328,9 +3327,11 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" s="2"/>
+      <c r="Y12" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="Z12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3369,16 +3370,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3386,10 +3387,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3403,7 +3404,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3412,16 +3413,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3447,11 +3448,13 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="Y13" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="Z13" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
@@ -3469,7 +3472,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3490,13 +3493,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3507,10 +3510,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3524,7 +3527,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3533,13 +3536,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3566,11 +3569,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="Z14" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3588,7 +3593,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3597,7 +3602,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>179</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3609,27 +3614,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AP14" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AQ14" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3652,13 +3657,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3709,7 +3714,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3736,7 +3741,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3747,10 +3752,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3779,7 +3784,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3820,19 +3825,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3859,7 +3864,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3870,10 +3875,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3896,19 +3901,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3957,7 +3962,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3981,10 +3986,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -3995,10 +4000,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4021,19 +4026,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4082,7 +4087,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4097,7 +4102,7 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>80</v>
@@ -4106,10 +4111,10 @@
         <v>80</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4120,14 +4125,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>216</v>
+        <v>80</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4137,7 +4142,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4203,7 +4208,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4379,7 +4384,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4442,7 +4447,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>232</v>
@@ -4740,13 +4745,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4878,7 +4883,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -4913,7 +4918,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>264</v>
@@ -5243,13 +5248,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5300,7 +5305,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5327,7 +5332,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5370,7 +5375,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5411,19 +5416,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5450,7 +5455,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5487,7 +5492,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>285</v>
@@ -5645,13 +5650,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5669,7 +5674,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5707,10 +5712,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5736,13 +5741,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5792,7 +5797,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5819,7 +5824,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5830,10 +5835,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5856,16 +5861,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5915,7 +5920,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5930,7 +5935,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5953,10 +5958,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5979,13 +5984,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6036,7 +6041,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6051,7 +6056,7 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>80</v>
@@ -6060,24 +6065,24 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6100,13 +6105,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6157,7 +6162,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6181,10 +6186,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6195,10 +6200,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6221,13 +6226,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6254,13 +6259,13 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
@@ -6278,7 +6283,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6293,7 +6298,7 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>80</v>
@@ -6302,24 +6307,24 @@
         <v>80</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6342,13 +6347,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6375,13 +6380,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6399,7 +6404,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6423,24 +6428,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6463,13 +6468,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6520,7 +6525,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6547,7 +6552,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6558,10 +6563,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6590,7 +6595,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -6631,19 +6636,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6670,7 +6675,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6681,10 +6686,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6707,19 +6712,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6768,7 +6773,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6792,10 +6797,10 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6806,10 +6811,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6832,19 +6837,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6893,7 +6898,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6908,7 +6913,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6917,10 +6922,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6931,10 +6936,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6957,13 +6962,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7014,7 +7019,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7038,10 +7043,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7052,10 +7057,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7078,13 +7083,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7135,7 +7140,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7156,13 +7161,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7173,10 +7178,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7199,13 +7204,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7256,7 +7261,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7283,7 +7288,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7294,10 +7299,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7326,7 +7331,7 @@
         <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>140</v>
@@ -7379,7 +7384,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7406,7 +7411,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7417,14 +7422,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7446,10 +7451,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7504,7 +7509,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7542,10 +7547,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7568,13 +7573,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7601,13 +7606,13 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>177</v>
+        <v>294</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
@@ -7625,7 +7630,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7646,13 +7651,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7663,10 +7668,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7689,16 +7694,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7748,7 +7753,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7769,16 +7774,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7786,10 +7791,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7812,13 +7817,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7869,7 +7874,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7890,13 +7895,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7907,10 +7912,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7933,13 +7938,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7966,13 +7971,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -7990,7 +7995,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8011,13 +8016,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8028,10 +8033,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8054,13 +8059,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8111,7 +8116,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8132,7 +8137,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8149,10 +8154,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8178,20 +8183,20 @@
         <v>253</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8236,7 +8241,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8260,7 +8265,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8274,10 +8279,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8300,13 +8305,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8333,13 +8338,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8357,7 +8362,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8395,10 +8400,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8421,13 +8426,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8478,7 +8483,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8490,7 +8495,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8516,10 +8521,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8542,13 +8547,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8599,7 +8604,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8626,7 +8631,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8637,10 +8642,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8669,7 +8674,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8722,7 +8727,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8749,7 +8754,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8760,14 +8765,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8789,10 +8794,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8847,7 +8852,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8885,10 +8890,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8911,13 +8916,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8968,7 +8973,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8992,7 +8997,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9006,10 +9011,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9035,10 +9040,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9089,7 +9094,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9127,10 +9132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9156,10 +9161,10 @@
         <v>245</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9210,7 +9215,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9234,7 +9239,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9248,10 +9253,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9277,10 +9282,10 @@
         <v>245</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9331,7 +9336,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9355,7 +9360,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9369,10 +9374,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9395,13 +9400,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9428,13 +9433,13 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
@@ -9452,7 +9457,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9476,7 +9481,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9490,10 +9495,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9516,13 +9521,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9549,13 +9554,13 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
@@ -9573,7 +9578,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9611,10 +9616,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9637,16 +9642,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9696,7 +9701,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9720,10 +9725,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9734,10 +9739,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9760,13 +9765,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9817,7 +9822,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9844,7 +9849,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9855,10 +9860,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9887,7 +9892,7 @@
         <v>138</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9940,7 +9945,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9967,7 +9972,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9978,14 +9983,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10007,10 +10012,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10065,7 +10070,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10103,10 +10108,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10132,10 +10137,10 @@
         <v>245</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10186,7 +10191,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10210,7 +10215,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>240</v>
@@ -10224,10 +10229,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10250,13 +10255,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10307,7 +10312,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10331,10 +10336,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10345,10 +10350,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10374,10 +10379,10 @@
         <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10428,7 +10433,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10452,10 +10457,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10466,10 +10471,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10492,13 +10497,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10549,7 +10554,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10587,10 +10592,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10613,13 +10618,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10670,7 +10675,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10697,7 +10702,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -10708,10 +10713,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10740,7 +10745,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10793,7 +10798,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10820,7 +10825,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -10831,14 +10836,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10860,10 +10865,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10918,7 +10923,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10956,10 +10961,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10982,13 +10987,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11039,7 +11044,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11077,10 +11082,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11106,10 +11111,10 @@
         <v>276</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11160,7 +11165,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11198,10 +11203,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11224,13 +11229,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11257,13 +11262,13 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
@@ -11281,7 +11286,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11319,10 +11324,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11345,16 +11350,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11399,10 +11404,10 @@
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11440,13 +11445,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11468,16 +11473,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11527,7 +11532,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11542,7 +11547,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11565,10 +11570,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11591,16 +11596,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11650,7 +11655,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3130" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for ADERS to Immunization</t>
+    <t>This StructureDefinition contains the maps for ADERS to us-core-immunization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Immunization</t>
+    <t>http://hl7.org/fhir/us/core/StructureDefinition/us-core-immunization</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -274,11 +274,11 @@
     <t>Immunization event information</t>
   </si>
   <si>
-    <t>Describes the event of a patient being administered a vaccine or a record of an immunization as reported by a patient, a clinician or another party.</t>
+    <t>\-</t>
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}us-core-5:SHOULD have a translation to the NDC value set {vaccineCode.coding.where(system='http://hl7.org/fhir/sid/ndc').empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -517,10 +517,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A set of codes indicating the current status of an Immunization.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/immunization-status|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/immunization-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -551,9 +548,6 @@
     <t>example</t>
   </si>
   <si>
-    <t>The reason why a vaccine was not administered.</t>
-  </si>
-  <si>
     <t>http://hl7.org/fhir/ValueSet/immunization-status-reason</t>
   </si>
   <si>
@@ -566,16 +560,20 @@
     <t>Immunization.vaccineCode</t>
   </si>
   <si>
-    <t>Vaccine product administered</t>
+    <t>Vaccine Product Type (bind to CVX)</t>
   </si>
   <si>
     <t>Vaccine that was administered or was to be administered.</t>
   </si>
   <si>
-    <t>The code for vaccine product administered.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/vaccine-code</t>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://cts.nlm.nih.gov/fhir/ValueSet/2.16.840.1.113762.1.4.1010.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us-core-5
+</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -677,7 +675,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1920: source value from ADERS - PVac1_TypeBrand (A-22.11)</t>
+    <t>1920: source value from ADERS - 22_PVac1_TypeBrand</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
@@ -689,7 +687,11 @@
     <t>Immunization.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Patient
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>
@@ -781,7 +783,7 @@
 </t>
   </si>
   <si>
-    <t>1926: source value from ADERS - PVac1_Date (A-22.17)</t>
+    <t>1926: source value from ADERS - 22_PVac1_Date</t>
   </si>
   <si>
     <t>Immunization.recorded</t>
@@ -928,9 +930,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -978,7 +977,7 @@
     <t>Reference.display</t>
   </si>
   <si>
-    <t>1921: source value from ADERS - PVac1_Mfgr (A-22.12)</t>
+    <t>1921: source value from ADERS - 22_PVac1_Mfgr</t>
   </si>
   <si>
     <t>Immunization.lotNumber</t>
@@ -990,7 +989,7 @@
     <t>Lot number of the  vaccine product.</t>
   </si>
   <si>
-    <t>1922: source value from ADERS - PVac1_Lot (A-22.13)</t>
+    <t>1922: source value from ADERS - 22_PVac1_Lot</t>
   </si>
   <si>
     <t>RXA-15</t>
@@ -1036,7 +1035,7 @@
     <t>http://hl7.org/fhir/ValueSet/immunization-site</t>
   </si>
   <si>
-    <t>1924: source value from ADERS - PVac1_Site (A-22.15)</t>
+    <t>1924: source value from ADERS - 22_PVac1_Site</t>
   </si>
   <si>
     <t>RXR-2</t>
@@ -1084,7 +1083,7 @@
     <t>Immunization.route.text</t>
   </si>
   <si>
-    <t>1923: source value from ADERS - PVac1_Route (A-22.14)</t>
+    <t>1923: source value from ADERS - 22_PVac1_Route</t>
   </si>
   <si>
     <t>Immunization.doseQuantity</t>
@@ -1532,7 +1531,7 @@
     <t>doseNumberString</t>
   </si>
   <si>
-    <t>1925: source value from ADERS - PVac1_DoseInSeries (A-22.16)</t>
+    <t>1925: source value from ADERS - 22_PVac1_DoseInSeries</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.seriesDoses[x]</t>
@@ -1871,7 +1870,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.07421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.61328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1886,7 +1885,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.7265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.24609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.8515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -2072,7 +2071,9 @@
       <c r="M2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="N2" s="2"/>
+      <c r="N2" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
         <v>80</v>
@@ -3281,7 +3282,7 @@
         <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>92</v>
@@ -3327,11 +3328,9 @@
       <c r="X12" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Y12" s="2"/>
+      <c r="Z12" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3370,16 +3369,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AN12" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO12" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AN12" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO12" t="s" s="2">
+      <c r="AP12" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="AP12" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="AQ12" t="s" s="2">
         <v>80</v>
@@ -3387,10 +3386,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3404,7 +3403,7 @@
         <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>80</v>
@@ -3413,16 +3412,16 @@
         <v>80</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3448,14 +3447,12 @@
         <v>80</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y13" s="2"/>
+      <c r="Z13" t="s" s="2">
         <v>171</v>
       </c>
-      <c r="Y13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>173</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>80</v>
       </c>
@@ -3472,7 +3469,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -3493,13 +3490,13 @@
         <v>80</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AP13" t="s" s="2">
         <v>80</v>
@@ -3510,10 +3507,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3527,7 +3524,7 @@
         <v>91</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>80</v>
@@ -3536,13 +3533,13 @@
         <v>92</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3569,13 +3566,11 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -3593,7 +3588,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>91</v>
@@ -3602,7 +3597,7 @@
         <v>91</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>179</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>103</v>
@@ -3614,27 +3609,27 @@
         <v>80</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AN14" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AN14" t="s" s="2">
+      <c r="AO14" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="AO14" t="s" s="2">
+      <c r="AP14" t="s" s="2">
         <v>183</v>
       </c>
-      <c r="AP14" t="s" s="2">
+      <c r="AQ14" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="AQ14" t="s" s="2">
-        <v>185</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3657,13 +3652,13 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3714,7 +3709,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3741,7 +3736,7 @@
         <v>80</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>80</v>
@@ -3752,10 +3747,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3784,7 +3779,7 @@
         <v>138</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>140</v>
@@ -3825,19 +3820,19 @@
         <v>80</v>
       </c>
       <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC16" t="s" s="2">
+      <c r="AD16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD16" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE16" t="s" s="2">
+      <c r="AF16" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3864,7 +3859,7 @@
         <v>80</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
@@ -3875,10 +3870,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3901,19 +3896,19 @@
         <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -3962,7 +3957,7 @@
         <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3986,10 +3981,10 @@
         <v>80</v>
       </c>
       <c r="AN17" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>80</v>
@@ -4000,10 +3995,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4026,19 +4021,19 @@
         <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N18" t="s" s="2">
+      <c r="O18" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4087,7 +4082,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4102,19 +4097,19 @@
         <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="AL18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4125,14 +4120,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4142,7 +4137,7 @@
         <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>80</v>
@@ -4208,7 +4203,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>91</v>
@@ -4384,7 +4379,7 @@
         <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>80</v>
@@ -4447,7 +4442,7 @@
         <v>80</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>232</v>
@@ -4745,13 +4740,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>80</v>
@@ -4883,7 +4878,7 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>261</v>
@@ -4918,7 +4913,7 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y25" t="s" s="2">
         <v>264</v>
@@ -5248,13 +5243,13 @@
         <v>80</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5305,7 +5300,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5332,7 +5327,7 @@
         <v>80</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>80</v>
@@ -5375,7 +5370,7 @@
         <v>138</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>140</v>
@@ -5416,19 +5411,19 @@
         <v>80</v>
       </c>
       <c r="AB29" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC29" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC29" t="s" s="2">
+      <c r="AD29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE29" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD29" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE29" t="s" s="2">
+      <c r="AF29" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5455,7 +5450,7 @@
         <v>80</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>80</v>
@@ -5492,7 +5487,7 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>285</v>
@@ -5650,31 +5645,31 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="Y31" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="Y31" t="s" s="2">
+      <c r="Z31" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="Z31" t="s" s="2">
+      <c r="AA31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5712,10 +5707,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5741,13 +5736,13 @@
         <v>149</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5797,7 +5792,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5824,7 +5819,7 @@
         <v>80</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>80</v>
@@ -5835,10 +5830,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5861,16 +5856,16 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5920,7 +5915,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5935,7 +5930,7 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>80</v>
@@ -5958,10 +5953,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5984,13 +5979,13 @@
         <v>80</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6041,7 +6036,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6056,33 +6051,33 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AP34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ34" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6105,13 +6100,13 @@
         <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>320</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6162,7 +6157,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6186,10 +6181,10 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AO35" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>80</v>
@@ -6200,10 +6195,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6226,13 +6221,13 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>324</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6259,14 +6254,14 @@
         <v>80</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>80</v>
       </c>
@@ -6283,7 +6278,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6298,33 +6293,33 @@
         <v>103</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AO36" t="s" s="2">
+      <c r="AP36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ36" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ36" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6347,13 +6342,13 @@
         <v>80</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6380,14 +6375,14 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="Z37" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="Z37" t="s" s="2">
-        <v>336</v>
-      </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6404,7 +6399,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6428,24 +6423,24 @@
         <v>80</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AO37" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="AO37" t="s" s="2">
+      <c r="AP37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>339</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6468,13 +6463,13 @@
         <v>80</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6525,7 +6520,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6552,7 +6547,7 @@
         <v>80</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>80</v>
@@ -6563,10 +6558,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6595,7 +6590,7 @@
         <v>138</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>140</v>
@@ -6636,19 +6631,19 @@
         <v>80</v>
       </c>
       <c r="AB39" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC39" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="AC39" t="s" s="2">
+      <c r="AD39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE39" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="AD39" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE39" t="s" s="2">
+      <c r="AF39" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6675,7 +6670,7 @@
         <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>80</v>
@@ -6686,10 +6681,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6712,19 +6707,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -6773,7 +6768,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6797,10 +6792,10 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="AO40" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>80</v>
@@ -6811,10 +6806,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6837,19 +6832,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -6898,7 +6893,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6913,7 +6908,7 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>80</v>
@@ -6922,10 +6917,10 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AO41" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>215</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>80</v>
@@ -6936,10 +6931,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6962,13 +6957,13 @@
         <v>80</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7019,7 +7014,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7043,10 +7038,10 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AO42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AO42" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>80</v>
@@ -7057,10 +7052,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7083,13 +7078,13 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7140,7 +7135,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7161,13 +7156,13 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7178,10 +7173,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7204,13 +7199,13 @@
         <v>80</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7261,7 +7256,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7288,7 +7283,7 @@
         <v>80</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7299,10 +7294,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7331,7 +7326,7 @@
         <v>138</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N45" t="s" s="2">
         <v>140</v>
@@ -7384,7 +7379,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7411,7 +7406,7 @@
         <v>80</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7422,14 +7417,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7451,10 +7446,10 @@
         <v>137</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>140</v>
@@ -7509,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7547,10 +7542,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7573,13 +7568,13 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7606,14 +7601,14 @@
         <v>80</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>294</v>
+        <v>177</v>
       </c>
       <c r="Y47" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="Z47" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="Z47" t="s" s="2">
-        <v>369</v>
-      </c>
       <c r="AA47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7630,7 +7625,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7651,13 +7646,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO47" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>371</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -7668,10 +7663,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7694,16 +7689,16 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7753,7 +7748,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>91</v>
@@ -7774,16 +7769,16 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AN48" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO48" t="s" s="2">
+      <c r="AP48" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>80</v>
@@ -7791,10 +7786,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7817,13 +7812,13 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7874,7 +7869,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7895,13 +7890,13 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AN49" t="s" s="2">
+      <c r="AO49" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>80</v>
@@ -7912,10 +7907,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7938,13 +7933,13 @@
         <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7971,14 +7966,14 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z50" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z50" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
       </c>
@@ -7995,7 +7990,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8016,13 +8011,13 @@
         <v>80</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AO50" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
@@ -8033,10 +8028,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8059,13 +8054,13 @@
         <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8116,7 +8111,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8137,7 +8132,7 @@
         <v>80</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8154,10 +8149,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8183,20 +8178,20 @@
         <v>253</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R52" t="s" s="2">
         <v>80</v>
@@ -8241,7 +8236,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8265,7 +8260,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>134</v>
@@ -8279,10 +8274,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8305,13 +8300,13 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8338,14 +8333,14 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y53" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z53" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z53" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
       </c>
@@ -8362,7 +8357,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8400,10 +8395,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8426,13 +8421,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8483,7 +8478,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8495,7 +8490,7 @@
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
@@ -8521,10 +8516,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8547,13 +8542,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8604,7 +8599,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8631,7 +8626,7 @@
         <v>80</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
@@ -8642,10 +8637,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8674,7 +8669,7 @@
         <v>138</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>140</v>
@@ -8727,7 +8722,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8754,7 +8749,7 @@
         <v>80</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>80</v>
@@ -8765,14 +8760,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8794,10 +8789,10 @@
         <v>137</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>140</v>
@@ -8852,7 +8847,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8890,10 +8885,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8916,13 +8911,13 @@
         <v>80</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8973,7 +8968,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8997,7 +8992,7 @@
         <v>80</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>134</v>
@@ -9011,10 +9006,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9040,10 +9035,10 @@
         <v>105</v>
       </c>
       <c r="L59" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9094,7 +9089,7 @@
         <v>80</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9132,10 +9127,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9161,10 +9156,10 @@
         <v>245</v>
       </c>
       <c r="L60" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9215,7 +9210,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9239,7 +9234,7 @@
         <v>80</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>134</v>
@@ -9253,10 +9248,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9282,10 +9277,10 @@
         <v>245</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9336,7 +9331,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9360,7 +9355,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>134</v>
@@ -9374,10 +9369,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9400,13 +9395,13 @@
         <v>80</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M62" t="s" s="2">
         <v>432</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>433</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9433,14 +9428,14 @@
         <v>80</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y62" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="Z62" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="Z62" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AA62" t="s" s="2">
         <v>80</v>
       </c>
@@ -9457,7 +9452,7 @@
         <v>80</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9481,7 +9476,7 @@
         <v>80</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>134</v>
@@ -9495,10 +9490,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9521,13 +9516,13 @@
         <v>80</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9554,14 +9549,14 @@
         <v>80</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="Z63" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="Z63" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="AA63" t="s" s="2">
         <v>80</v>
       </c>
@@ -9578,7 +9573,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9616,10 +9611,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9642,16 +9637,16 @@
         <v>80</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9701,7 +9696,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9725,10 +9720,10 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AO64" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>80</v>
@@ -9739,10 +9734,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9765,13 +9760,13 @@
         <v>80</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L65" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L65" t="s" s="2">
+      <c r="M65" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9822,7 +9817,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9849,7 +9844,7 @@
         <v>80</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>80</v>
@@ -9860,10 +9855,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9892,7 +9887,7 @@
         <v>138</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>140</v>
@@ -9945,7 +9940,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9972,7 +9967,7 @@
         <v>80</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>80</v>
@@ -9983,14 +9978,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10012,10 +10007,10 @@
         <v>137</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>140</v>
@@ -10070,7 +10065,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10108,10 +10103,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10137,10 +10132,10 @@
         <v>245</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10191,7 +10186,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10215,7 +10210,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>240</v>
@@ -10229,10 +10224,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10255,13 +10250,13 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10312,7 +10307,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10336,10 +10331,10 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AO69" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>80</v>
@@ -10350,10 +10345,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10379,10 +10374,10 @@
         <v>253</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10433,7 +10428,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10457,10 +10452,10 @@
         <v>80</v>
       </c>
       <c r="AN70" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AO70" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>80</v>
@@ -10471,10 +10466,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10497,13 +10492,13 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10554,7 +10549,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10592,10 +10587,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10618,13 +10613,13 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="M72" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10675,7 +10670,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10702,7 +10697,7 @@
         <v>80</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>80</v>
@@ -10713,10 +10708,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10745,7 +10740,7 @@
         <v>138</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>140</v>
@@ -10798,7 +10793,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10825,7 +10820,7 @@
         <v>80</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>80</v>
@@ -10836,14 +10831,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -10865,10 +10860,10 @@
         <v>137</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>140</v>
@@ -10923,7 +10918,7 @@
         <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10961,10 +10956,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10987,13 +10982,13 @@
         <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L75" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11044,7 +11039,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11082,10 +11077,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11111,10 +11106,10 @@
         <v>276</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11165,7 +11160,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11203,10 +11198,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11229,13 +11224,13 @@
         <v>80</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11262,14 +11257,14 @@
         <v>80</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="Z77" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="Z77" t="s" s="2">
-        <v>482</v>
-      </c>
       <c r="AA77" t="s" s="2">
         <v>80</v>
       </c>
@@ -11286,7 +11281,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11324,10 +11319,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11350,16 +11345,16 @@
         <v>80</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M78" t="s" s="2">
+      <c r="N78" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11404,10 +11399,10 @@
         <v>80</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>91</v>
@@ -11445,13 +11440,13 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>80</v>
@@ -11473,16 +11468,16 @@
         <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="M79" t="s" s="2">
+      <c r="N79" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11532,7 +11527,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>91</v>
@@ -11547,7 +11542,7 @@
         <v>103</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>80</v>
@@ -11570,10 +11565,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11596,16 +11591,16 @@
         <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="M80" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="N80" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11655,7 +11650,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>

--- a/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization-pvac1.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
